--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>92348</v>
+        <v>92351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136146422</v>
       </c>
       <c r="B14" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136146428</v>
       </c>
       <c r="B15" t="n">
-        <v>91111</v>
+        <v>91113</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>92351</v>
+        <v>92352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 32004-2026 artfynd.xlsx
+++ b/artfynd/A 32004-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136146424</v>
       </c>
       <c r="B2" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136146435</v>
       </c>
       <c r="B3" t="n">
-        <v>92352</v>
+        <v>92357</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136146432</v>
       </c>
       <c r="B7" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136146442</v>
       </c>
       <c r="B8" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>136146422</v>
       </c>
       <c r="B14" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>136146428</v>
       </c>
       <c r="B15" t="n">
-        <v>91113</v>
+        <v>91115</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         <v>136146434</v>
       </c>
       <c r="B19" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         <v>136146425</v>
       </c>
       <c r="B24" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         <v>136146439</v>
       </c>
       <c r="B25" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>136146420</v>
       </c>
       <c r="B31" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>136146430</v>
       </c>
       <c r="B32" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>136146436</v>
       </c>
       <c r="B33" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -6677,7 +6677,7 @@
         <v>136146441</v>
       </c>
       <c r="B54" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         <v>136146423</v>
       </c>
       <c r="B59" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>136146427</v>
       </c>
       <c r="B62" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>136146431</v>
       </c>
       <c r="B64" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
